--- a/data/HGT-inserts_summary_filtered.xlsx
+++ b/data/HGT-inserts_summary_filtered.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maximadams/Desktop/Work/RA/Blaberidae_genomics/hgt/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kyleewart/Documents/PostDoc/HGT_pipeline/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C77BAD8F-4773-B34F-8DE7-2DC2A4BF3C40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A0B48C7-5770-DE46-8532-3FE97C812C57}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="23120" windowHeight="16380" xr2:uid="{3365DD2C-654A-1041-91AD-AF43EE6D7734}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="23120" windowHeight="16360" xr2:uid="{3365DD2C-654A-1041-91AD-AF43EE6D7734}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="46">
   <si>
     <t>Genome</t>
   </si>
@@ -153,20 +153,23 @@
     <t># inserts</t>
   </si>
   <si>
-    <t># no contaminants</t>
-  </si>
-  <si>
-    <t># no assembly duplicates</t>
-  </si>
-  <si>
     <t># no tranpsposed duplicates</t>
+  </si>
+  <si>
+    <t>After removing putative contaminants</t>
+  </si>
+  <si>
+    <t>After removing putative false duplicates</t>
+  </si>
+  <si>
+    <t>After removing repetitive/low-complexity regions</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -539,17 +542,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EAA4914-59B0-C040-B32C-FA53996F591F}">
-  <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="33.1640625" customWidth="1"/>
     <col min="2" max="2" width="56.33203125" customWidth="1"/>
     <col min="4" max="4" width="16.6640625" customWidth="1"/>
-    <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="26.83203125" customWidth="1"/>
+    <col min="5" max="5" width="37" customWidth="1"/>
+    <col min="6" max="6" width="43.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -560,16 +564,19 @@
         <v>41</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -585,11 +592,11 @@
       <c r="E2">
         <v>649</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <v>595</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -605,11 +612,11 @@
       <c r="E3">
         <v>580</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <v>548</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -625,11 +632,11 @@
       <c r="E4">
         <v>13</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -645,11 +652,11 @@
       <c r="E5">
         <v>5</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -665,11 +672,11 @@
       <c r="E6">
         <v>601</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <v>595</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -685,11 +692,11 @@
       <c r="E7">
         <v>4814</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <v>4782</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -705,11 +712,11 @@
       <c r="E8">
         <v>5367</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <v>5324</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -725,11 +732,11 @@
       <c r="E9">
         <v>5005</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <v>4944</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -745,11 +752,11 @@
       <c r="E10">
         <v>3031</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <v>2981</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" t="s">
         <v>1</v>
       </c>
@@ -765,11 +772,11 @@
       <c r="E11">
         <v>1667</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <v>1632</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -785,11 +792,11 @@
       <c r="E12">
         <v>4077</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <v>4054</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -805,11 +812,11 @@
       <c r="E13">
         <v>1737</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <v>1722</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -825,11 +832,11 @@
       <c r="E14">
         <v>3205</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <v>3131</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -845,11 +852,11 @@
       <c r="E15">
         <v>3942</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <v>3906</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -865,11 +872,11 @@
       <c r="E16">
         <v>4533</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <v>4457</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -885,11 +892,11 @@
       <c r="E17">
         <v>4353</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <v>4239</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -905,11 +912,11 @@
       <c r="E18">
         <v>331</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <v>323</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -925,11 +932,11 @@
       <c r="E19">
         <v>139</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <v>127</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -945,11 +952,11 @@
       <c r="E20">
         <v>710</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <v>693</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" t="s">
         <v>11</v>
       </c>
@@ -965,11 +972,11 @@
       <c r="E21">
         <v>711</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <v>702</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -985,11 +992,11 @@
       <c r="E22">
         <v>8</v>
       </c>
-      <c r="F22">
+      <c r="G22">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" t="s">
         <v>29</v>
       </c>
@@ -1005,11 +1012,11 @@
       <c r="E23">
         <v>4</v>
       </c>
-      <c r="F23">
+      <c r="G23">
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -1025,12 +1032,12 @@
       <c r="E24">
         <v>82</v>
       </c>
-      <c r="F24">
+      <c r="G24">
         <v>68</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F24">
+  <sortState ref="A2:G24">
     <sortCondition ref="A2:A24"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
